--- a/Borsdata - Export/ARFA-Arctic Falls.xlsx
+++ b/Borsdata - Export/ARFA-Arctic Falls.xlsx
@@ -195,382 +195,388 @@
     <x:t>ISIN</x:t>
   </x:si>
   <x:si>
+    <x:t>2026-07-13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rullande 12 månader</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3 år</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Börsdata ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Industri</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quarter</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kvartal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sektor</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Stödtjänster &amp; Service</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bransch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>First North</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nyckeltal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lista</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sverige</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Land</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Aktier</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Instrument</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Q3 2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Senaste rapport</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Senaste aktiekurs</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Aktiekurs</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kursdatum</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2023</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PriceDay</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Daglig aktiekurshistorik</x:t>
+  </x:si>
+  <x:si>
+    <x:t>&gt;20 år</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Aktiekursvaluta</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2024</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PriceWeek</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Veckovis kurshistorik</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rapportvaluta</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PriceMonth</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Månadsvis kurshistorik</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Report</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nettoomsättning</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MSEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bruttoresultat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rörelseresultat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Resultat Före Skatt</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Resultat Hänföring Aktieägare</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Vinst/Aktie</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Antal Aktier</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Milj</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Utdelning</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Immateriella tillgångar</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Materiella tillgångar</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Finansiella tillgångar</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Summa Anläggningstillgångar</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kassa/Bank</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Summa Omsättningstillgångar</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Summa Tillgångar</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Summa Eget Kapital</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Långfristiga Skulder</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kortfristiga Skulder</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Summa Eget Kapital och Skulder</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nettoskuld</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kassaf LöpandeVerk</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kassaf Investeringsverk</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kassaf Finansieringsverk</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Åretskassaflöde</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FrittKassaflöde</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EBITDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Totala Skulder</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Totala Skulder och Eget kapital</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nettoomsättning/Aktie</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EBITDA / Aktie</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Eget Kapital/Aktie</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nettoskuld/Aktie</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Operativ kassaflöde/Aktie</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FCF / Aktie</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Årets kassaflöde/Aktie</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EBITDA-marginal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bruttomarginal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rörelsemarginal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Vinstmarginal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Immat.tillgång.-%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kassa-%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rörelsekapital-%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Soliditet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Avkastning På EK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Avkastning på T</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OP-marginal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Capex %</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FCF-marginal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Utdelning/FCF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Årets kassaflöde marginal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Aktiekurs Snitt</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Aktiekurs Högsta</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Aktiekurs Lägsta</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P/E</x:t>
+  </x:si>
+  <x:si>
+    <x:t>x</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P/S</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P/B</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Direktavkastning</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EV/EBIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EV/EBITDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EV/E</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EV/FCF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EV/OP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EV/S</x:t>
+  </x:si>
+  <x:si>
+    <x:t>E/EV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EBIT/EV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P/(E)x</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P/B-tang</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Date</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Openprice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Highprice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lowprice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Closeprice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Volume</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Highligted header</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Header</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Common value</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Highlighted value</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Q2 2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Q1 2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Q4 2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Q3 2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Q2 2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Q1 2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-10</x:t>
+  </x:si>
+  <x:si>
     <x:t>2026-07-09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rullande 12 månader</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3 år</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Börsdata ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Industri</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quarter</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kvartal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sektor</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Stödtjänster &amp; Service</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bransch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>First North</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Nyckeltal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Lista</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sverige</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Land</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Aktier</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Instrument</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Q3 2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Senaste rapport</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Senaste aktiekurs</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Aktiekurs</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kursdatum</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2023</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PriceDay</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Daglig aktiekurshistorik</x:t>
-  </x:si>
-  <x:si>
-    <x:t>&gt;20 år</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Aktiekursvaluta</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PriceWeek</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Veckovis kurshistorik</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rapportvaluta</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PriceMonth</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Månadsvis kurshistorik</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Report</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Nettoomsättning</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MSEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bruttoresultat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rörelseresultat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Resultat Före Skatt</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Resultat Hänföring Aktieägare</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Vinst/Aktie</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Antal Aktier</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Milj</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Utdelning</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Immateriella tillgångar</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Materiella tillgångar</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Finansiella tillgångar</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Summa Anläggningstillgångar</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kassa/Bank</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Summa Omsättningstillgångar</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Summa Tillgångar</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Summa Eget Kapital</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Långfristiga Skulder</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kortfristiga Skulder</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Summa Eget Kapital och Skulder</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Nettoskuld</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kassaf LöpandeVerk</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kassaf Investeringsverk</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kassaf Finansieringsverk</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Åretskassaflöde</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FrittKassaflöde</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EBITDA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Totala Skulder</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Totala Skulder och Eget kapital</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Nettoomsättning/Aktie</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EBITDA / Aktie</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Eget Kapital/Aktie</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Nettoskuld/Aktie</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Operativ kassaflöde/Aktie</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FCF / Aktie</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Årets kassaflöde/Aktie</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EBITDA-marginal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bruttomarginal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rörelsemarginal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Vinstmarginal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Immat.tillgång.-%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kassa-%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rörelsekapital-%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Soliditet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Avkastning På EK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Avkastning på T</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OP-marginal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Capex %</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FCF-marginal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Utdelning/FCF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Årets kassaflöde marginal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Aktiekurs Snitt</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Aktiekurs Högsta</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Aktiekurs Lägsta</x:t>
-  </x:si>
-  <x:si>
-    <x:t>P/E</x:t>
-  </x:si>
-  <x:si>
-    <x:t>x</x:t>
-  </x:si>
-  <x:si>
-    <x:t>P/S</x:t>
-  </x:si>
-  <x:si>
-    <x:t>P/B</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Direktavkastning</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EV/EBIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EV/EBITDA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EV/E</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EV/FCF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EV/OP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EV/S</x:t>
-  </x:si>
-  <x:si>
-    <x:t>E/EV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EBIT/EV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>P/(E)x</x:t>
-  </x:si>
-  <x:si>
-    <x:t>P/B-tang</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Date</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Openprice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Highprice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Lowprice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Closeprice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Volume</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Highligted header</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Header</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Common value</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Highlighted value</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-07-10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Q2 2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Q1 2026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Q4 2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Q3 2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Q2 2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Q1 2025</x:t>
   </x:si>
   <x:si>
     <x:t>2026-07-08</x:t>
@@ -4158,7 +4164,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C25" s="107">
-        <x:v>70.4</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="D25" s="79"/>
       <x:c r="E25" s="102" t="s">
@@ -6247,7 +6253,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L65" s="143">
-        <x:v>18.5540008544922</x:v>
+        <x:v>17.6840000152588</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:16075" x14ac:dyDescent="0.25">
@@ -6273,7 +6279,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L66" s="143">
-        <x:v>4.01599979400635</x:v>
+        <x:v>3.82800006866455</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:16075" x14ac:dyDescent="0.25">
@@ -6299,7 +6305,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L67" s="143">
-        <x:v>4.13100004196167</x:v>
+        <x:v>3.93700003623962</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:16075" x14ac:dyDescent="0.25">
@@ -6339,7 +6345,7 @@
       <x:c r="J69" s="139"/>
       <x:c r="K69" s="139"/>
       <x:c r="L69" s="143">
-        <x:v>15.7040004730225</x:v>
+        <x:v>15.0959997177124</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:16075" x14ac:dyDescent="0.25">
@@ -6359,7 +6365,7 @@
       <x:c r="J70" s="139"/>
       <x:c r="K70" s="139"/>
       <x:c r="L70" s="143">
-        <x:v>11.298999786377</x:v>
+        <x:v>10.8620004653931</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:16075" x14ac:dyDescent="0.25">
@@ -6379,7 +6385,7 @@
       <x:c r="J71" s="139"/>
       <x:c r="K71" s="139"/>
       <x:c r="L71" s="143">
-        <x:v>22.492000579834</x:v>
+        <x:v>21.6229991912842</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:16075" x14ac:dyDescent="0.25">
@@ -6399,7 +6405,7 @@
       <x:c r="J72" s="139"/>
       <x:c r="K72" s="139"/>
       <x:c r="L72" s="143">
-        <x:v>21.451000213623</x:v>
+        <x:v>20.6219997406006</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:16075" x14ac:dyDescent="0.25">
@@ -6425,7 +6431,7 @@
         <x:v>3.31599998474121</x:v>
       </x:c>
       <x:c r="L73" s="143">
-        <x:v>16.1979999542236</x:v>
+        <x:v>15.5710000991821</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:16075" x14ac:dyDescent="0.25">
@@ -6445,7 +6451,7 @@
       <x:c r="J74" s="139"/>
       <x:c r="K74" s="139"/>
       <x:c r="L74" s="143">
-        <x:v>4.86800003051758</x:v>
+        <x:v>4.67999982833862</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:16075" x14ac:dyDescent="0.25">
@@ -6465,7 +6471,7 @@
       <x:c r="J75" s="139"/>
       <x:c r="K75" s="139"/>
       <x:c r="L75" s="143">
-        <x:v>4.44600009918213</x:v>
+        <x:v>4.625</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:16075" x14ac:dyDescent="0.25">
@@ -6485,7 +6491,7 @@
       <x:c r="J76" s="139"/>
       <x:c r="K76" s="139"/>
       <x:c r="L76" s="143">
-        <x:v>6.36800003051758</x:v>
+        <x:v>6.62400007247925</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:16075" x14ac:dyDescent="0.25">
@@ -6507,7 +6513,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L77" s="143">
-        <x:v>18.0189990997314</x:v>
+        <x:v>17.173999786377</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:16075" x14ac:dyDescent="0.25">
@@ -6533,7 +6539,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L78" s="143">
-        <x:v>4.13299989700317</x:v>
+        <x:v>3.93899989128113</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:16075" x14ac:dyDescent="0.25">
@@ -9277,19 +9283,19 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B2" s="150">
-        <x:v>72.2</x:v>
+        <x:v>65.3</x:v>
       </x:c>
       <x:c r="C2" s="150">
-        <x:v>72.2</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="D2" s="150">
-        <x:v>66.3</x:v>
+        <x:v>65.1</x:v>
       </x:c>
       <x:c r="E2" s="151">
-        <x:v>70.4</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="F2" s="152">
-        <x:v>2829</x:v>
+        <x:v>2317</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:6">
@@ -9297,19 +9303,19 @@
         <x:v>153</x:v>
       </x:c>
       <x:c r="B3" s="150">
-        <x:v>69.4</x:v>
+        <x:v>70.6</x:v>
       </x:c>
       <x:c r="C3" s="150">
-        <x:v>69.4</x:v>
+        <x:v>70.6</x:v>
       </x:c>
       <x:c r="D3" s="150">
-        <x:v>69.4</x:v>
+        <x:v>65.1</x:v>
       </x:c>
       <x:c r="E3" s="151">
-        <x:v>69.4</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F3" s="152">
-        <x:v>170</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:6">
@@ -9323,13 +9329,13 @@
         <x:v>72.2</x:v>
       </x:c>
       <x:c r="D4" s="150">
-        <x:v>69.5</x:v>
+        <x:v>66.3</x:v>
       </x:c>
       <x:c r="E4" s="151">
-        <x:v>71.4</x:v>
+        <x:v>70.4</x:v>
       </x:c>
       <x:c r="F4" s="152">
-        <x:v>246</x:v>
+        <x:v>2829</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:6">
@@ -9337,19 +9343,19 @@
         <x:v>155</x:v>
       </x:c>
       <x:c r="B5" s="150">
-        <x:v>71.2</x:v>
+        <x:v>69.4</x:v>
       </x:c>
       <x:c r="C5" s="150">
-        <x:v>72.4</x:v>
+        <x:v>69.4</x:v>
       </x:c>
       <x:c r="D5" s="150">
-        <x:v>69.1</x:v>
+        <x:v>69.4</x:v>
       </x:c>
       <x:c r="E5" s="151">
-        <x:v>72.3</x:v>
+        <x:v>69.4</x:v>
       </x:c>
       <x:c r="F5" s="152">
-        <x:v>484</x:v>
+        <x:v>170</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:6">
@@ -9357,19 +9363,19 @@
         <x:v>156</x:v>
       </x:c>
       <x:c r="B6" s="150">
-        <x:v>71.2</x:v>
+        <x:v>72.2</x:v>
       </x:c>
       <x:c r="C6" s="150">
-        <x:v>71.2</x:v>
+        <x:v>72.2</x:v>
       </x:c>
       <x:c r="D6" s="150">
-        <x:v>69</x:v>
+        <x:v>69.5</x:v>
       </x:c>
       <x:c r="E6" s="151">
-        <x:v>71.2</x:v>
+        <x:v>71.4</x:v>
       </x:c>
       <x:c r="F6" s="152">
-        <x:v>475</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:6">
@@ -9377,19 +9383,19 @@
         <x:v>157</x:v>
       </x:c>
       <x:c r="B7" s="150">
-        <x:v>66.4</x:v>
+        <x:v>71.2</x:v>
       </x:c>
       <x:c r="C7" s="150">
-        <x:v>71.2</x:v>
+        <x:v>72.4</x:v>
       </x:c>
       <x:c r="D7" s="150">
-        <x:v>66.4</x:v>
+        <x:v>69.1</x:v>
       </x:c>
       <x:c r="E7" s="151">
-        <x:v>71.2</x:v>
+        <x:v>72.3</x:v>
       </x:c>
       <x:c r="F7" s="152">
-        <x:v>1865</x:v>
+        <x:v>484</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:6">
@@ -9397,19 +9403,19 @@
         <x:v>158</x:v>
       </x:c>
       <x:c r="B8" s="150">
-        <x:v>68.5</x:v>
+        <x:v>71.2</x:v>
       </x:c>
       <x:c r="C8" s="150">
-        <x:v>68.6</x:v>
+        <x:v>71.2</x:v>
       </x:c>
       <x:c r="D8" s="150">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E8" s="151">
-        <x:v>68.6</x:v>
+        <x:v>71.2</x:v>
       </x:c>
       <x:c r="F8" s="152">
-        <x:v>388</x:v>
+        <x:v>475</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:6">
@@ -9420,16 +9426,16 @@
         <x:v>66.4</x:v>
       </x:c>
       <x:c r="C9" s="150">
-        <x:v>68.6</x:v>
+        <x:v>71.2</x:v>
       </x:c>
       <x:c r="D9" s="150">
-        <x:v>65</x:v>
+        <x:v>66.4</x:v>
       </x:c>
       <x:c r="E9" s="151">
-        <x:v>68.6</x:v>
+        <x:v>71.2</x:v>
       </x:c>
       <x:c r="F9" s="152">
-        <x:v>214</x:v>
+        <x:v>1865</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:6">
@@ -9437,19 +9443,19 @@
         <x:v>160</x:v>
       </x:c>
       <x:c r="B10" s="150">
-        <x:v>66</x:v>
+        <x:v>68.5</x:v>
       </x:c>
       <x:c r="C10" s="150">
-        <x:v>66.8</x:v>
+        <x:v>68.6</x:v>
       </x:c>
       <x:c r="D10" s="150">
-        <x:v>64</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E10" s="151">
-        <x:v>66.6</x:v>
+        <x:v>68.6</x:v>
       </x:c>
       <x:c r="F10" s="152">
-        <x:v>2314</x:v>
+        <x:v>388</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:6">
@@ -9457,19 +9463,19 @@
         <x:v>161</x:v>
       </x:c>
       <x:c r="B11" s="150">
-        <x:v>68.1</x:v>
+        <x:v>66.4</x:v>
       </x:c>
       <x:c r="C11" s="150">
-        <x:v>68.1</x:v>
+        <x:v>68.6</x:v>
       </x:c>
       <x:c r="D11" s="150">
-        <x:v>65.8</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E11" s="151">
-        <x:v>66.9</x:v>
+        <x:v>68.6</x:v>
       </x:c>
       <x:c r="F11" s="152">
-        <x:v>391</x:v>
+        <x:v>214</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:6">
@@ -9477,19 +9483,19 @@
         <x:v>162</x:v>
       </x:c>
       <x:c r="B12" s="150">
-        <x:v>65.8</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C12" s="150">
-        <x:v>68.5</x:v>
+        <x:v>66.8</x:v>
       </x:c>
       <x:c r="D12" s="150">
-        <x:v>65.1</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E12" s="151">
-        <x:v>68.2</x:v>
+        <x:v>66.6</x:v>
       </x:c>
       <x:c r="F12" s="152">
-        <x:v>460</x:v>
+        <x:v>2314</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:6">
@@ -9497,19 +9503,19 @@
         <x:v>163</x:v>
       </x:c>
       <x:c r="B13" s="150">
-        <x:v>68.7</x:v>
+        <x:v>68.1</x:v>
       </x:c>
       <x:c r="C13" s="150">
-        <x:v>68.7</x:v>
+        <x:v>68.1</x:v>
       </x:c>
       <x:c r="D13" s="150">
-        <x:v>64.6</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="E13" s="151">
-        <x:v>65.8</x:v>
+        <x:v>66.9</x:v>
       </x:c>
       <x:c r="F13" s="152">
-        <x:v>2410</x:v>
+        <x:v>391</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:6">
@@ -9517,19 +9523,19 @@
         <x:v>164</x:v>
       </x:c>
       <x:c r="B14" s="150">
-        <x:v>64.6</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="C14" s="150">
-        <x:v>68.9</x:v>
+        <x:v>68.5</x:v>
       </x:c>
       <x:c r="D14" s="150">
-        <x:v>64.6</x:v>
+        <x:v>65.1</x:v>
       </x:c>
       <x:c r="E14" s="151">
-        <x:v>68.5</x:v>
+        <x:v>68.2</x:v>
       </x:c>
       <x:c r="F14" s="152">
-        <x:v>175</x:v>
+        <x:v>460</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:6">
@@ -9537,19 +9543,19 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="B15" s="150">
-        <x:v>66</x:v>
+        <x:v>68.7</x:v>
       </x:c>
       <x:c r="C15" s="150">
-        <x:v>66</x:v>
+        <x:v>68.7</x:v>
       </x:c>
       <x:c r="D15" s="150">
         <x:v>64.6</x:v>
       </x:c>
       <x:c r="E15" s="151">
-        <x:v>65.9</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F15" s="152">
-        <x:v>1461</x:v>
+        <x:v>2410</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:6">
@@ -9557,19 +9563,19 @@
         <x:v>166</x:v>
       </x:c>
       <x:c r="B16" s="150">
-        <x:v>69</x:v>
+        <x:v>64.6</x:v>
       </x:c>
       <x:c r="C16" s="150">
-        <x:v>69</x:v>
+        <x:v>68.9</x:v>
       </x:c>
       <x:c r="D16" s="150">
-        <x:v>64.3</x:v>
+        <x:v>64.6</x:v>
       </x:c>
       <x:c r="E16" s="151">
-        <x:v>65.9</x:v>
+        <x:v>68.5</x:v>
       </x:c>
       <x:c r="F16" s="152">
-        <x:v>1268</x:v>
+        <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:6">
@@ -9577,19 +9583,19 @@
         <x:v>167</x:v>
       </x:c>
       <x:c r="B17" s="150">
-        <x:v>66.8</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C17" s="150">
-        <x:v>68.5</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D17" s="150">
-        <x:v>65.5</x:v>
+        <x:v>64.6</x:v>
       </x:c>
       <x:c r="E17" s="151">
-        <x:v>68.5</x:v>
+        <x:v>65.9</x:v>
       </x:c>
       <x:c r="F17" s="152">
-        <x:v>2672</x:v>
+        <x:v>1461</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:6">
@@ -9597,19 +9603,19 @@
         <x:v>168</x:v>
       </x:c>
       <x:c r="B18" s="150">
-        <x:v>67.4</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C18" s="150">
-        <x:v>67.4</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D18" s="150">
-        <x:v>65</x:v>
+        <x:v>64.3</x:v>
       </x:c>
       <x:c r="E18" s="151">
-        <x:v>66.4</x:v>
+        <x:v>65.9</x:v>
       </x:c>
       <x:c r="F18" s="152">
-        <x:v>809</x:v>
+        <x:v>1268</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:6">
@@ -9617,19 +9623,19 @@
         <x:v>169</x:v>
       </x:c>
       <x:c r="B19" s="150">
-        <x:v>68.4</x:v>
+        <x:v>66.8</x:v>
       </x:c>
       <x:c r="C19" s="150">
-        <x:v>68.4</x:v>
+        <x:v>68.5</x:v>
       </x:c>
       <x:c r="D19" s="150">
-        <x:v>64.5</x:v>
+        <x:v>65.5</x:v>
       </x:c>
       <x:c r="E19" s="151">
-        <x:v>65</x:v>
+        <x:v>68.5</x:v>
       </x:c>
       <x:c r="F19" s="152">
-        <x:v>869</x:v>
+        <x:v>2672</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:6">
@@ -9637,19 +9643,19 @@
         <x:v>170</x:v>
       </x:c>
       <x:c r="B20" s="150">
-        <x:v>67.3</x:v>
+        <x:v>67.4</x:v>
       </x:c>
       <x:c r="C20" s="150">
-        <x:v>68.4</x:v>
+        <x:v>67.4</x:v>
       </x:c>
       <x:c r="D20" s="150">
-        <x:v>64.9</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E20" s="151">
-        <x:v>68.2</x:v>
+        <x:v>66.4</x:v>
       </x:c>
       <x:c r="F20" s="152">
-        <x:v>419</x:v>
+        <x:v>809</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:6">
@@ -9657,19 +9663,19 @@
         <x:v>171</x:v>
       </x:c>
       <x:c r="B21" s="150">
+        <x:v>68.4</x:v>
+      </x:c>
+      <x:c r="C21" s="150">
+        <x:v>68.4</x:v>
+      </x:c>
+      <x:c r="D21" s="150">
+        <x:v>64.5</x:v>
+      </x:c>
+      <x:c r="E21" s="151">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="C21" s="150">
-        <x:v>67.3</x:v>
-      </x:c>
-      <x:c r="D21" s="150">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E21" s="151">
-        <x:v>67.3</x:v>
-      </x:c>
       <x:c r="F21" s="152">
-        <x:v>312</x:v>
+        <x:v>869</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:6">
@@ -9677,19 +9683,19 @@
         <x:v>172</x:v>
       </x:c>
       <x:c r="B22" s="150">
-        <x:v>65.3</x:v>
+        <x:v>67.3</x:v>
       </x:c>
       <x:c r="C22" s="150">
-        <x:v>67.4</x:v>
+        <x:v>68.4</x:v>
       </x:c>
       <x:c r="D22" s="150">
-        <x:v>65.3</x:v>
+        <x:v>64.9</x:v>
       </x:c>
       <x:c r="E22" s="151">
-        <x:v>67.4</x:v>
+        <x:v>68.2</x:v>
       </x:c>
       <x:c r="F22" s="152">
-        <x:v>1259</x:v>
+        <x:v>419</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:6">
@@ -9697,19 +9703,19 @@
         <x:v>173</x:v>
       </x:c>
       <x:c r="B23" s="150">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C23" s="150">
-        <x:v>67</x:v>
+        <x:v>67.3</x:v>
       </x:c>
       <x:c r="D23" s="150">
-        <x:v>65.1</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E23" s="151">
-        <x:v>65.3</x:v>
+        <x:v>67.3</x:v>
       </x:c>
       <x:c r="F23" s="152">
-        <x:v>20236</x:v>
+        <x:v>312</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:6">
@@ -9717,19 +9723,19 @@
         <x:v>174</x:v>
       </x:c>
       <x:c r="B24" s="150">
-        <x:v>66.1</x:v>
+        <x:v>65.3</x:v>
       </x:c>
       <x:c r="C24" s="150">
-        <x:v>69.6</x:v>
+        <x:v>67.4</x:v>
       </x:c>
       <x:c r="D24" s="150">
-        <x:v>64.7</x:v>
+        <x:v>65.3</x:v>
       </x:c>
       <x:c r="E24" s="151">
-        <x:v>64.7</x:v>
+        <x:v>67.4</x:v>
       </x:c>
       <x:c r="F24" s="152">
-        <x:v>1951</x:v>
+        <x:v>1259</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:6">
@@ -9737,19 +9743,19 @@
         <x:v>175</x:v>
       </x:c>
       <x:c r="B25" s="150">
-        <x:v>67.8</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C25" s="150">
-        <x:v>67.8</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D25" s="150">
-        <x:v>66.1</x:v>
+        <x:v>65.1</x:v>
       </x:c>
       <x:c r="E25" s="151">
-        <x:v>66.1</x:v>
+        <x:v>65.3</x:v>
       </x:c>
       <x:c r="F25" s="152">
-        <x:v>277</x:v>
+        <x:v>20236</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:6">
@@ -9757,19 +9763,19 @@
         <x:v>176</x:v>
       </x:c>
       <x:c r="B26" s="150">
-        <x:v>69.8</x:v>
+        <x:v>66.1</x:v>
       </x:c>
       <x:c r="C26" s="150">
-        <x:v>69.8</x:v>
+        <x:v>69.6</x:v>
       </x:c>
       <x:c r="D26" s="150">
-        <x:v>64.5</x:v>
+        <x:v>64.7</x:v>
       </x:c>
       <x:c r="E26" s="151">
-        <x:v>67.8</x:v>
+        <x:v>64.7</x:v>
       </x:c>
       <x:c r="F26" s="152">
-        <x:v>873</x:v>
+        <x:v>1951</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:6">
@@ -9777,19 +9783,19 @@
         <x:v>177</x:v>
       </x:c>
       <x:c r="B27" s="150">
-        <x:v>70</x:v>
+        <x:v>67.8</x:v>
       </x:c>
       <x:c r="C27" s="150">
-        <x:v>73</x:v>
+        <x:v>67.8</x:v>
       </x:c>
       <x:c r="D27" s="150">
-        <x:v>64</x:v>
+        <x:v>66.1</x:v>
       </x:c>
       <x:c r="E27" s="151">
-        <x:v>69.9</x:v>
+        <x:v>66.1</x:v>
       </x:c>
       <x:c r="F27" s="152">
-        <x:v>3258</x:v>
+        <x:v>277</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:6">
@@ -9803,13 +9809,13 @@
         <x:v>69.8</x:v>
       </x:c>
       <x:c r="D28" s="150">
-        <x:v>66.8</x:v>
+        <x:v>64.5</x:v>
       </x:c>
       <x:c r="E28" s="151">
-        <x:v>69.7</x:v>
+        <x:v>67.8</x:v>
       </x:c>
       <x:c r="F28" s="152">
-        <x:v>38012</x:v>
+        <x:v>873</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:6">
@@ -9817,19 +9823,19 @@
         <x:v>179</x:v>
       </x:c>
       <x:c r="B29" s="150">
-        <x:v>71.2</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C29" s="150">
-        <x:v>71.2</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D29" s="150">
-        <x:v>67.3</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E29" s="151">
-        <x:v>70</x:v>
+        <x:v>69.9</x:v>
       </x:c>
       <x:c r="F29" s="152">
-        <x:v>2766</x:v>
+        <x:v>3258</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:6">
@@ -9837,19 +9843,19 @@
         <x:v>180</x:v>
       </x:c>
       <x:c r="B30" s="150">
-        <x:v>70.7</x:v>
+        <x:v>69.8</x:v>
       </x:c>
       <x:c r="C30" s="150">
-        <x:v>71</x:v>
+        <x:v>69.8</x:v>
       </x:c>
       <x:c r="D30" s="150">
-        <x:v>67.6</x:v>
+        <x:v>66.8</x:v>
       </x:c>
       <x:c r="E30" s="151">
-        <x:v>70</x:v>
+        <x:v>69.7</x:v>
       </x:c>
       <x:c r="F30" s="152">
-        <x:v>12270</x:v>
+        <x:v>38012</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:6">
@@ -9857,19 +9863,19 @@
         <x:v>181</x:v>
       </x:c>
       <x:c r="B31" s="150">
-        <x:v>63.1</x:v>
+        <x:v>71.2</x:v>
       </x:c>
       <x:c r="C31" s="150">
-        <x:v>72.5</x:v>
+        <x:v>71.2</x:v>
       </x:c>
       <x:c r="D31" s="150">
-        <x:v>62.6</x:v>
+        <x:v>67.3</x:v>
       </x:c>
       <x:c r="E31" s="151">
-        <x:v>70.7</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F31" s="152">
-        <x:v>22299</x:v>
+        <x:v>2766</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:6">
@@ -9877,19 +9883,19 @@
         <x:v>182</x:v>
       </x:c>
       <x:c r="B32" s="150">
-        <x:v>64.3</x:v>
+        <x:v>70.7</x:v>
       </x:c>
       <x:c r="C32" s="150">
-        <x:v>64.6</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D32" s="150">
-        <x:v>64</x:v>
+        <x:v>67.6</x:v>
       </x:c>
       <x:c r="E32" s="151">
-        <x:v>64.6</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F32" s="152">
-        <x:v>3840</x:v>
+        <x:v>12270</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:6">
@@ -9897,19 +9903,19 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="B33" s="150">
-        <x:v>64.4</x:v>
+        <x:v>63.1</x:v>
       </x:c>
       <x:c r="C33" s="150">
-        <x:v>65.5</x:v>
+        <x:v>72.5</x:v>
       </x:c>
       <x:c r="D33" s="150">
-        <x:v>64.3</x:v>
+        <x:v>62.6</x:v>
       </x:c>
       <x:c r="E33" s="151">
-        <x:v>64.6</x:v>
+        <x:v>70.7</x:v>
       </x:c>
       <x:c r="F33" s="152">
-        <x:v>1697</x:v>
+        <x:v>22299</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:6">
@@ -9917,19 +9923,19 @@
         <x:v>184</x:v>
       </x:c>
       <x:c r="B34" s="150">
-        <x:v>64</x:v>
+        <x:v>64.3</x:v>
       </x:c>
       <x:c r="C34" s="150">
-        <x:v>65.7</x:v>
+        <x:v>64.6</x:v>
       </x:c>
       <x:c r="D34" s="150">
         <x:v>64</x:v>
       </x:c>
       <x:c r="E34" s="151">
-        <x:v>64.5</x:v>
+        <x:v>64.6</x:v>
       </x:c>
       <x:c r="F34" s="152">
-        <x:v>9139</x:v>
+        <x:v>3840</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:6">
@@ -9937,19 +9943,19 @@
         <x:v>185</x:v>
       </x:c>
       <x:c r="B35" s="150">
-        <x:v>65.2</x:v>
+        <x:v>64.4</x:v>
       </x:c>
       <x:c r="C35" s="150">
-        <x:v>65.6</x:v>
+        <x:v>65.5</x:v>
       </x:c>
       <x:c r="D35" s="150">
-        <x:v>64</x:v>
+        <x:v>64.3</x:v>
       </x:c>
       <x:c r="E35" s="151">
-        <x:v>64.3</x:v>
+        <x:v>64.6</x:v>
       </x:c>
       <x:c r="F35" s="152">
-        <x:v>6379</x:v>
+        <x:v>1697</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:6">
@@ -9957,19 +9963,19 @@
         <x:v>186</x:v>
       </x:c>
       <x:c r="B36" s="150">
-        <x:v>66.5</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C36" s="150">
-        <x:v>67.2</x:v>
+        <x:v>65.7</x:v>
       </x:c>
       <x:c r="D36" s="150">
-        <x:v>64.7</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E36" s="151">
-        <x:v>65.1</x:v>
+        <x:v>64.5</x:v>
       </x:c>
       <x:c r="F36" s="152">
-        <x:v>4393</x:v>
+        <x:v>9139</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:6">
@@ -9977,19 +9983,19 @@
         <x:v>187</x:v>
       </x:c>
       <x:c r="B37" s="150">
-        <x:v>67.5</x:v>
+        <x:v>65.2</x:v>
       </x:c>
       <x:c r="C37" s="150">
-        <x:v>67.5</x:v>
+        <x:v>65.6</x:v>
       </x:c>
       <x:c r="D37" s="150">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E37" s="151">
-        <x:v>66</x:v>
+        <x:v>64.3</x:v>
       </x:c>
       <x:c r="F37" s="152">
-        <x:v>11577</x:v>
+        <x:v>6379</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:6">
@@ -9997,19 +10003,19 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="B38" s="150">
-        <x:v>69.9</x:v>
+        <x:v>66.5</x:v>
       </x:c>
       <x:c r="C38" s="150">
-        <x:v>69.9</x:v>
+        <x:v>67.2</x:v>
       </x:c>
       <x:c r="D38" s="150">
-        <x:v>67.5</x:v>
+        <x:v>64.7</x:v>
       </x:c>
       <x:c r="E38" s="151">
-        <x:v>68.5</x:v>
+        <x:v>65.1</x:v>
       </x:c>
       <x:c r="F38" s="152">
-        <x:v>2152</x:v>
+        <x:v>4393</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:6">
@@ -10017,19 +10023,19 @@
         <x:v>189</x:v>
       </x:c>
       <x:c r="B39" s="150">
-        <x:v>69.8</x:v>
+        <x:v>67.5</x:v>
       </x:c>
       <x:c r="C39" s="150">
-        <x:v>70.3</x:v>
+        <x:v>67.5</x:v>
       </x:c>
       <x:c r="D39" s="150">
-        <x:v>68.7</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E39" s="151">
-        <x:v>68.7</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F39" s="152">
-        <x:v>1422</x:v>
+        <x:v>11577</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:6">
@@ -10037,19 +10043,19 @@
         <x:v>190</x:v>
       </x:c>
       <x:c r="B40" s="150">
-        <x:v>69.5</x:v>
+        <x:v>69.9</x:v>
       </x:c>
       <x:c r="C40" s="150">
-        <x:v>70</x:v>
+        <x:v>69.9</x:v>
       </x:c>
       <x:c r="D40" s="150">
-        <x:v>68.2</x:v>
+        <x:v>67.5</x:v>
       </x:c>
       <x:c r="E40" s="151">
-        <x:v>69.4</x:v>
+        <x:v>68.5</x:v>
       </x:c>
       <x:c r="F40" s="152">
-        <x:v>9324</x:v>
+        <x:v>2152</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:6">
@@ -10057,19 +10063,19 @@
         <x:v>191</x:v>
       </x:c>
       <x:c r="B41" s="150">
-        <x:v>71.2</x:v>
+        <x:v>69.8</x:v>
       </x:c>
       <x:c r="C41" s="150">
-        <x:v>71.2</x:v>
+        <x:v>70.3</x:v>
       </x:c>
       <x:c r="D41" s="150">
-        <x:v>68.1</x:v>
+        <x:v>68.7</x:v>
       </x:c>
       <x:c r="E41" s="151">
-        <x:v>69.5</x:v>
+        <x:v>68.7</x:v>
       </x:c>
       <x:c r="F41" s="152">
-        <x:v>6825</x:v>
+        <x:v>1422</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:6">
@@ -10077,19 +10083,19 @@
         <x:v>192</x:v>
       </x:c>
       <x:c r="B42" s="150">
-        <x:v>73.4</x:v>
+        <x:v>69.5</x:v>
       </x:c>
       <x:c r="C42" s="150">
-        <x:v>73.4</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D42" s="150">
-        <x:v>65.6</x:v>
+        <x:v>68.2</x:v>
       </x:c>
       <x:c r="E42" s="151">
-        <x:v>71.2</x:v>
+        <x:v>69.4</x:v>
       </x:c>
       <x:c r="F42" s="152">
-        <x:v>30823</x:v>
+        <x:v>9324</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:6">
@@ -10097,19 +10103,19 @@
         <x:v>193</x:v>
       </x:c>
       <x:c r="B43" s="150">
-        <x:v>72</x:v>
+        <x:v>71.2</x:v>
       </x:c>
       <x:c r="C43" s="150">
-        <x:v>75.8</x:v>
+        <x:v>71.2</x:v>
       </x:c>
       <x:c r="D43" s="150">
-        <x:v>71.5</x:v>
+        <x:v>68.1</x:v>
       </x:c>
       <x:c r="E43" s="151">
-        <x:v>75.8</x:v>
+        <x:v>69.5</x:v>
       </x:c>
       <x:c r="F43" s="152">
-        <x:v>8938</x:v>
+        <x:v>6825</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:6">
@@ -10117,19 +10123,19 @@
         <x:v>194</x:v>
       </x:c>
       <x:c r="B44" s="150">
-        <x:v>72.8</x:v>
+        <x:v>73.4</x:v>
       </x:c>
       <x:c r="C44" s="150">
-        <x:v>73.6</x:v>
+        <x:v>73.4</x:v>
       </x:c>
       <x:c r="D44" s="150">
-        <x:v>70.8</x:v>
+        <x:v>65.6</x:v>
       </x:c>
       <x:c r="E44" s="151">
-        <x:v>72.8</x:v>
+        <x:v>71.2</x:v>
       </x:c>
       <x:c r="F44" s="152">
-        <x:v>5654</x:v>
+        <x:v>30823</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:6">
@@ -10137,19 +10143,19 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="B45" s="150">
-        <x:v>72.2</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C45" s="150">
-        <x:v>73</x:v>
+        <x:v>75.8</x:v>
       </x:c>
       <x:c r="D45" s="150">
-        <x:v>72.2</x:v>
+        <x:v>71.5</x:v>
       </x:c>
       <x:c r="E45" s="151">
-        <x:v>72.2</x:v>
+        <x:v>75.8</x:v>
       </x:c>
       <x:c r="F45" s="152">
-        <x:v>4691</x:v>
+        <x:v>8938</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:6">
@@ -10157,19 +10163,19 @@
         <x:v>196</x:v>
       </x:c>
       <x:c r="B46" s="150">
-        <x:v>71.9</x:v>
+        <x:v>72.8</x:v>
       </x:c>
       <x:c r="C46" s="150">
-        <x:v>72.2</x:v>
+        <x:v>73.6</x:v>
       </x:c>
       <x:c r="D46" s="150">
-        <x:v>70.4</x:v>
+        <x:v>70.8</x:v>
       </x:c>
       <x:c r="E46" s="151">
-        <x:v>71.8</x:v>
+        <x:v>72.8</x:v>
       </x:c>
       <x:c r="F46" s="152">
-        <x:v>2828</x:v>
+        <x:v>5654</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:6">
@@ -10177,19 +10183,19 @@
         <x:v>197</x:v>
       </x:c>
       <x:c r="B47" s="150">
-        <x:v>69.1</x:v>
+        <x:v>72.2</x:v>
       </x:c>
       <x:c r="C47" s="150">
-        <x:v>71.4</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D47" s="150">
-        <x:v>69</x:v>
+        <x:v>72.2</x:v>
       </x:c>
       <x:c r="E47" s="151">
-        <x:v>70</x:v>
+        <x:v>72.2</x:v>
       </x:c>
       <x:c r="F47" s="152">
-        <x:v>9231</x:v>
+        <x:v>4691</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:6">
@@ -10197,19 +10203,19 @@
         <x:v>198</x:v>
       </x:c>
       <x:c r="B48" s="150">
-        <x:v>72</x:v>
+        <x:v>71.9</x:v>
       </x:c>
       <x:c r="C48" s="150">
-        <x:v>72.1</x:v>
+        <x:v>72.2</x:v>
       </x:c>
       <x:c r="D48" s="150">
-        <x:v>69.1</x:v>
+        <x:v>70.4</x:v>
       </x:c>
       <x:c r="E48" s="151">
-        <x:v>70.7</x:v>
+        <x:v>71.8</x:v>
       </x:c>
       <x:c r="F48" s="152">
-        <x:v>9544</x:v>
+        <x:v>2828</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:6">
@@ -10217,19 +10223,19 @@
         <x:v>199</x:v>
       </x:c>
       <x:c r="B49" s="150">
-        <x:v>71.9</x:v>
+        <x:v>69.1</x:v>
       </x:c>
       <x:c r="C49" s="150">
-        <x:v>72.7</x:v>
+        <x:v>71.4</x:v>
       </x:c>
       <x:c r="D49" s="150">
-        <x:v>71.2</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E49" s="151">
-        <x:v>72.2</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F49" s="152">
-        <x:v>864</x:v>
+        <x:v>9231</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:6">
@@ -10237,19 +10243,19 @@
         <x:v>200</x:v>
       </x:c>
       <x:c r="B50" s="150">
-        <x:v>73.2</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C50" s="150">
-        <x:v>73.3</x:v>
+        <x:v>72.1</x:v>
       </x:c>
       <x:c r="D50" s="150">
-        <x:v>71.5</x:v>
+        <x:v>69.1</x:v>
       </x:c>
       <x:c r="E50" s="151">
-        <x:v>71.9</x:v>
+        <x:v>70.7</x:v>
       </x:c>
       <x:c r="F50" s="152">
-        <x:v>6901</x:v>
+        <x:v>9544</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:6">
@@ -10257,19 +10263,19 @@
         <x:v>201</x:v>
       </x:c>
       <x:c r="B51" s="150">
-        <x:v>74</x:v>
+        <x:v>71.9</x:v>
       </x:c>
       <x:c r="C51" s="150">
-        <x:v>74.2</x:v>
+        <x:v>72.7</x:v>
       </x:c>
       <x:c r="D51" s="150">
+        <x:v>71.2</x:v>
+      </x:c>
+      <x:c r="E51" s="151">
         <x:v>72.2</x:v>
       </x:c>
-      <x:c r="E51" s="151">
-        <x:v>73.3</x:v>
-      </x:c>
       <x:c r="F51" s="152">
-        <x:v>855</x:v>
+        <x:v>864</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:6">
@@ -10277,19 +10283,19 @@
         <x:v>202</x:v>
       </x:c>
       <x:c r="B52" s="150">
-        <x:v>73.8</x:v>
+        <x:v>73.2</x:v>
       </x:c>
       <x:c r="C52" s="150">
-        <x:v>75.1</x:v>
+        <x:v>73.3</x:v>
       </x:c>
       <x:c r="D52" s="150">
-        <x:v>72.4</x:v>
+        <x:v>71.5</x:v>
       </x:c>
       <x:c r="E52" s="151">
-        <x:v>74</x:v>
+        <x:v>71.9</x:v>
       </x:c>
       <x:c r="F52" s="152">
-        <x:v>6696</x:v>
+        <x:v>6901</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:6">
@@ -10297,19 +10303,19 @@
         <x:v>203</x:v>
       </x:c>
       <x:c r="B53" s="150">
-        <x:v>74.9</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C53" s="150">
-        <x:v>74.9</x:v>
+        <x:v>74.2</x:v>
       </x:c>
       <x:c r="D53" s="150">
-        <x:v>72.9</x:v>
+        <x:v>72.2</x:v>
       </x:c>
       <x:c r="E53" s="151">
-        <x:v>73.9</x:v>
+        <x:v>73.3</x:v>
       </x:c>
       <x:c r="F53" s="152">
-        <x:v>686</x:v>
+        <x:v>855</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:6">
@@ -10317,19 +10323,19 @@
         <x:v>204</x:v>
       </x:c>
       <x:c r="B54" s="150">
-        <x:v>74.9</x:v>
+        <x:v>73.8</x:v>
       </x:c>
       <x:c r="C54" s="150">
-        <x:v>76.9</x:v>
+        <x:v>75.1</x:v>
       </x:c>
       <x:c r="D54" s="150">
+        <x:v>72.4</x:v>
+      </x:c>
+      <x:c r="E54" s="151">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="E54" s="151">
-        <x:v>74.3</x:v>
-      </x:c>
       <x:c r="F54" s="152">
-        <x:v>4750</x:v>
+        <x:v>6696</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:6">
@@ -10337,19 +10343,19 @@
         <x:v>205</x:v>
       </x:c>
       <x:c r="B55" s="150">
-        <x:v>73.3</x:v>
+        <x:v>74.9</x:v>
       </x:c>
       <x:c r="C55" s="150">
-        <x:v>74.4</x:v>
+        <x:v>74.9</x:v>
       </x:c>
       <x:c r="D55" s="150">
-        <x:v>72.2</x:v>
+        <x:v>72.9</x:v>
       </x:c>
       <x:c r="E55" s="151">
-        <x:v>74.2</x:v>
+        <x:v>73.9</x:v>
       </x:c>
       <x:c r="F55" s="152">
-        <x:v>3317</x:v>
+        <x:v>686</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:6">
@@ -10357,19 +10363,19 @@
         <x:v>206</x:v>
       </x:c>
       <x:c r="B56" s="150">
-        <x:v>72.9</x:v>
+        <x:v>74.9</x:v>
       </x:c>
       <x:c r="C56" s="150">
-        <x:v>74.7</x:v>
+        <x:v>76.9</x:v>
       </x:c>
       <x:c r="D56" s="150">
-        <x:v>72.4</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E56" s="151">
-        <x:v>72.5</x:v>
+        <x:v>74.3</x:v>
       </x:c>
       <x:c r="F56" s="152">
-        <x:v>7281</x:v>
+        <x:v>4750</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:6">
@@ -10377,19 +10383,19 @@
         <x:v>207</x:v>
       </x:c>
       <x:c r="B57" s="150">
-        <x:v>72.6</x:v>
+        <x:v>73.3</x:v>
       </x:c>
       <x:c r="C57" s="150">
-        <x:v>73.7</x:v>
+        <x:v>74.4</x:v>
       </x:c>
       <x:c r="D57" s="150">
         <x:v>72.2</x:v>
       </x:c>
       <x:c r="E57" s="151">
-        <x:v>73.5</x:v>
+        <x:v>74.2</x:v>
       </x:c>
       <x:c r="F57" s="152">
-        <x:v>1957</x:v>
+        <x:v>3317</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:6">
@@ -10397,19 +10403,19 @@
         <x:v>208</x:v>
       </x:c>
       <x:c r="B58" s="150">
-        <x:v>73.9</x:v>
+        <x:v>72.9</x:v>
       </x:c>
       <x:c r="C58" s="150">
-        <x:v>73.9</x:v>
+        <x:v>74.7</x:v>
       </x:c>
       <x:c r="D58" s="150">
+        <x:v>72.4</x:v>
+      </x:c>
+      <x:c r="E58" s="151">
         <x:v>72.5</x:v>
       </x:c>
-      <x:c r="E58" s="151">
-        <x:v>72.8</x:v>
-      </x:c>
       <x:c r="F58" s="152">
-        <x:v>4021</x:v>
+        <x:v>7281</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:6">
@@ -10417,19 +10423,19 @@
         <x:v>209</x:v>
       </x:c>
       <x:c r="B59" s="150">
-        <x:v>73</x:v>
+        <x:v>72.6</x:v>
       </x:c>
       <x:c r="C59" s="150">
-        <x:v>73.9</x:v>
+        <x:v>73.7</x:v>
       </x:c>
       <x:c r="D59" s="150">
-        <x:v>71.9</x:v>
+        <x:v>72.2</x:v>
       </x:c>
       <x:c r="E59" s="151">
-        <x:v>73.9</x:v>
+        <x:v>73.5</x:v>
       </x:c>
       <x:c r="F59" s="152">
-        <x:v>664</x:v>
+        <x:v>1957</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:6">
@@ -10437,19 +10443,19 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="B60" s="150">
-        <x:v>71.7</x:v>
+        <x:v>73.9</x:v>
       </x:c>
       <x:c r="C60" s="150">
-        <x:v>74.9</x:v>
+        <x:v>73.9</x:v>
       </x:c>
       <x:c r="D60" s="150">
-        <x:v>71.7</x:v>
+        <x:v>72.5</x:v>
       </x:c>
       <x:c r="E60" s="151">
-        <x:v>73.5</x:v>
+        <x:v>72.8</x:v>
       </x:c>
       <x:c r="F60" s="152">
-        <x:v>7116</x:v>
+        <x:v>4021</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:6">
@@ -10457,19 +10463,19 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B61" s="150">
-        <x:v>70.4</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C61" s="150">
-        <x:v>71.8</x:v>
+        <x:v>73.9</x:v>
       </x:c>
       <x:c r="D61" s="150">
-        <x:v>70.4</x:v>
+        <x:v>71.9</x:v>
       </x:c>
       <x:c r="E61" s="151">
-        <x:v>71.4</x:v>
+        <x:v>73.9</x:v>
       </x:c>
       <x:c r="F61" s="152">
-        <x:v>1314</x:v>
+        <x:v>664</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:6">
@@ -10477,19 +10483,19 @@
         <x:v>212</x:v>
       </x:c>
       <x:c r="B62" s="150">
-        <x:v>72</x:v>
+        <x:v>71.7</x:v>
       </x:c>
       <x:c r="C62" s="150">
-        <x:v>72.6</x:v>
+        <x:v>74.9</x:v>
       </x:c>
       <x:c r="D62" s="150">
-        <x:v>70.3</x:v>
+        <x:v>71.7</x:v>
       </x:c>
       <x:c r="E62" s="151">
-        <x:v>70.5</x:v>
+        <x:v>73.5</x:v>
       </x:c>
       <x:c r="F62" s="152">
-        <x:v>7360</x:v>
+        <x:v>7116</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:6">
@@ -10497,19 +10503,19 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="B63" s="150">
-        <x:v>72.2</x:v>
+        <x:v>70.4</x:v>
       </x:c>
       <x:c r="C63" s="150">
-        <x:v>72.7</x:v>
+        <x:v>71.8</x:v>
       </x:c>
       <x:c r="D63" s="150">
-        <x:v>71.2</x:v>
+        <x:v>70.4</x:v>
       </x:c>
       <x:c r="E63" s="151">
-        <x:v>72.7</x:v>
+        <x:v>71.4</x:v>
       </x:c>
       <x:c r="F63" s="152">
-        <x:v>1886</x:v>
+        <x:v>1314</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:6">
@@ -10517,19 +10523,19 @@
         <x:v>214</x:v>
       </x:c>
       <x:c r="B64" s="150">
-        <x:v>72.4</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C64" s="150">
-        <x:v>73.5</x:v>
+        <x:v>72.6</x:v>
       </x:c>
       <x:c r="D64" s="150">
-        <x:v>72.2</x:v>
+        <x:v>70.3</x:v>
       </x:c>
       <x:c r="E64" s="151">
-        <x:v>72.2</x:v>
+        <x:v>70.5</x:v>
       </x:c>
       <x:c r="F64" s="152">
-        <x:v>588</x:v>
+        <x:v>7360</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:6">
@@ -10537,19 +10543,19 @@
         <x:v>215</x:v>
       </x:c>
       <x:c r="B65" s="150">
-        <x:v>72.1</x:v>
+        <x:v>72.2</x:v>
       </x:c>
       <x:c r="C65" s="150">
-        <x:v>72.5</x:v>
+        <x:v>72.7</x:v>
       </x:c>
       <x:c r="D65" s="150">
-        <x:v>71.6</x:v>
+        <x:v>71.2</x:v>
       </x:c>
       <x:c r="E65" s="151">
-        <x:v>71.9</x:v>
+        <x:v>72.7</x:v>
       </x:c>
       <x:c r="F65" s="152">
-        <x:v>7387</x:v>
+        <x:v>1886</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:6">
@@ -10557,19 +10563,19 @@
         <x:v>216</x:v>
       </x:c>
       <x:c r="B66" s="150">
-        <x:v>72.9</x:v>
+        <x:v>72.4</x:v>
       </x:c>
       <x:c r="C66" s="150">
-        <x:v>72.9</x:v>
+        <x:v>73.5</x:v>
       </x:c>
       <x:c r="D66" s="150">
-        <x:v>71</x:v>
+        <x:v>72.2</x:v>
       </x:c>
       <x:c r="E66" s="151">
-        <x:v>71</x:v>
+        <x:v>72.2</x:v>
       </x:c>
       <x:c r="F66" s="152">
-        <x:v>4419</x:v>
+        <x:v>588</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:6">
@@ -10577,19 +10583,19 @@
         <x:v>217</x:v>
       </x:c>
       <x:c r="B67" s="150">
-        <x:v>71.5</x:v>
+        <x:v>72.1</x:v>
       </x:c>
       <x:c r="C67" s="150">
-        <x:v>73</x:v>
+        <x:v>72.5</x:v>
       </x:c>
       <x:c r="D67" s="150">
-        <x:v>71.5</x:v>
+        <x:v>71.6</x:v>
       </x:c>
       <x:c r="E67" s="151">
-        <x:v>72.9</x:v>
+        <x:v>71.9</x:v>
       </x:c>
       <x:c r="F67" s="152">
-        <x:v>658</x:v>
+        <x:v>7387</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:6">
@@ -10597,19 +10603,19 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="B68" s="150">
-        <x:v>73.3</x:v>
+        <x:v>72.9</x:v>
       </x:c>
       <x:c r="C68" s="150">
-        <x:v>74.1</x:v>
+        <x:v>72.9</x:v>
       </x:c>
       <x:c r="D68" s="150">
-        <x:v>71.5</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E68" s="151">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F68" s="152">
-        <x:v>1606</x:v>
+        <x:v>4419</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:6">
@@ -10617,19 +10623,19 @@
         <x:v>219</x:v>
       </x:c>
       <x:c r="B69" s="150">
-        <x:v>74.6</x:v>
+        <x:v>71.5</x:v>
       </x:c>
       <x:c r="C69" s="150">
-        <x:v>74.6</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D69" s="150">
-        <x:v>71.2</x:v>
+        <x:v>71.5</x:v>
       </x:c>
       <x:c r="E69" s="151">
-        <x:v>71.2</x:v>
+        <x:v>72.9</x:v>
       </x:c>
       <x:c r="F69" s="152">
-        <x:v>2894</x:v>
+        <x:v>658</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:6">
@@ -10637,19 +10643,19 @@
         <x:v>220</x:v>
       </x:c>
       <x:c r="B70" s="150">
-        <x:v>75</x:v>
+        <x:v>73.3</x:v>
       </x:c>
       <x:c r="C70" s="150">
-        <x:v>75</x:v>
+        <x:v>74.1</x:v>
       </x:c>
       <x:c r="D70" s="150">
-        <x:v>72.5</x:v>
+        <x:v>71.5</x:v>
       </x:c>
       <x:c r="E70" s="151">
-        <x:v>73.6</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F70" s="152">
-        <x:v>2510</x:v>
+        <x:v>1606</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:6">
@@ -10657,19 +10663,19 @@
         <x:v>221</x:v>
       </x:c>
       <x:c r="B71" s="150">
-        <x:v>75.6</x:v>
+        <x:v>74.6</x:v>
       </x:c>
       <x:c r="C71" s="150">
-        <x:v>76.2</x:v>
+        <x:v>74.6</x:v>
       </x:c>
       <x:c r="D71" s="150">
-        <x:v>74.1</x:v>
+        <x:v>71.2</x:v>
       </x:c>
       <x:c r="E71" s="151">
-        <x:v>75</x:v>
+        <x:v>71.2</x:v>
       </x:c>
       <x:c r="F71" s="152">
-        <x:v>1415</x:v>
+        <x:v>2894</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:6">
@@ -10677,19 +10683,19 @@
         <x:v>222</x:v>
       </x:c>
       <x:c r="B72" s="150">
-        <x:v>75.7</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C72" s="150">
-        <x:v>75.7</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D72" s="150">
-        <x:v>73</x:v>
+        <x:v>72.5</x:v>
       </x:c>
       <x:c r="E72" s="151">
-        <x:v>75.7</x:v>
+        <x:v>73.6</x:v>
       </x:c>
       <x:c r="F72" s="152">
-        <x:v>1953</x:v>
+        <x:v>2510</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:6">
@@ -10697,19 +10703,19 @@
         <x:v>223</x:v>
       </x:c>
       <x:c r="B73" s="150">
-        <x:v>75.1</x:v>
+        <x:v>75.6</x:v>
       </x:c>
       <x:c r="C73" s="150">
-        <x:v>76.5</x:v>
+        <x:v>76.2</x:v>
       </x:c>
       <x:c r="D73" s="150">
-        <x:v>75.1</x:v>
+        <x:v>74.1</x:v>
       </x:c>
       <x:c r="E73" s="151">
-        <x:v>76.4</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="F73" s="152">
-        <x:v>250</x:v>
+        <x:v>1415</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:6">
@@ -10717,19 +10723,19 @@
         <x:v>224</x:v>
       </x:c>
       <x:c r="B74" s="150">
-        <x:v>74</x:v>
+        <x:v>75.7</x:v>
       </x:c>
       <x:c r="C74" s="150">
-        <x:v>78</x:v>
+        <x:v>75.7</x:v>
       </x:c>
       <x:c r="D74" s="150">
-        <x:v>74</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E74" s="151">
-        <x:v>77.3</x:v>
+        <x:v>75.7</x:v>
       </x:c>
       <x:c r="F74" s="152">
-        <x:v>1823</x:v>
+        <x:v>1953</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:6">
@@ -10737,19 +10743,19 @@
         <x:v>225</x:v>
       </x:c>
       <x:c r="B75" s="150">
-        <x:v>73.9</x:v>
+        <x:v>75.1</x:v>
       </x:c>
       <x:c r="C75" s="150">
-        <x:v>78</x:v>
+        <x:v>76.5</x:v>
       </x:c>
       <x:c r="D75" s="150">
-        <x:v>72.3</x:v>
+        <x:v>75.1</x:v>
       </x:c>
       <x:c r="E75" s="151">
-        <x:v>77.8</x:v>
+        <x:v>76.4</x:v>
       </x:c>
       <x:c r="F75" s="152">
-        <x:v>16730</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:6">
@@ -10760,16 +10766,16 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="C76" s="150">
-        <x:v>74.8</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D76" s="150">
-        <x:v>72.4</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E76" s="151">
-        <x:v>74</x:v>
+        <x:v>77.3</x:v>
       </x:c>
       <x:c r="F76" s="152">
-        <x:v>1572</x:v>
+        <x:v>1823</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:6">
@@ -10777,19 +10783,19 @@
         <x:v>227</x:v>
       </x:c>
       <x:c r="B77" s="150">
-        <x:v>74.2</x:v>
+        <x:v>73.9</x:v>
       </x:c>
       <x:c r="C77" s="150">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D77" s="150">
-        <x:v>74</x:v>
+        <x:v>72.3</x:v>
       </x:c>
       <x:c r="E77" s="151">
-        <x:v>74.8</x:v>
+        <x:v>77.8</x:v>
       </x:c>
       <x:c r="F77" s="152">
-        <x:v>1407</x:v>
+        <x:v>16730</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:6">
@@ -10797,19 +10803,19 @@
         <x:v>228</x:v>
       </x:c>
       <x:c r="B78" s="150">
-        <x:v>76</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C78" s="150">
-        <x:v>77.3</x:v>
+        <x:v>74.8</x:v>
       </x:c>
       <x:c r="D78" s="150">
-        <x:v>74.6</x:v>
+        <x:v>72.4</x:v>
       </x:c>
       <x:c r="E78" s="151">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F78" s="152">
-        <x:v>3384</x:v>
+        <x:v>1572</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:6">
@@ -10817,19 +10823,19 @@
         <x:v>229</x:v>
       </x:c>
       <x:c r="B79" s="150">
-        <x:v>75.1</x:v>
+        <x:v>74.2</x:v>
       </x:c>
       <x:c r="C79" s="150">
-        <x:v>76.4</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D79" s="150">
-        <x:v>74.1</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E79" s="151">
-        <x:v>75.6</x:v>
+        <x:v>74.8</x:v>
       </x:c>
       <x:c r="F79" s="152">
-        <x:v>3649</x:v>
+        <x:v>1407</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:6">
@@ -10837,19 +10843,19 @@
         <x:v>230</x:v>
       </x:c>
       <x:c r="B80" s="150">
-        <x:v>75.3</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C80" s="150">
-        <x:v>78</x:v>
+        <x:v>77.3</x:v>
       </x:c>
       <x:c r="D80" s="150">
-        <x:v>75.2</x:v>
+        <x:v>74.6</x:v>
       </x:c>
       <x:c r="E80" s="151">
-        <x:v>76.9</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="F80" s="152">
-        <x:v>2426</x:v>
+        <x:v>3384</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:6">
@@ -10863,13 +10869,13 @@
         <x:v>76.4</x:v>
       </x:c>
       <x:c r="D81" s="150">
-        <x:v>75.1</x:v>
+        <x:v>74.1</x:v>
       </x:c>
       <x:c r="E81" s="151">
         <x:v>75.6</x:v>
       </x:c>
       <x:c r="F81" s="152">
-        <x:v>903</x:v>
+        <x:v>3649</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:6">
@@ -10877,19 +10883,19 @@
         <x:v>232</x:v>
       </x:c>
       <x:c r="B82" s="150">
-        <x:v>77</x:v>
+        <x:v>75.3</x:v>
       </x:c>
       <x:c r="C82" s="150">
-        <x:v>77.4</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D82" s="150">
-        <x:v>75</x:v>
+        <x:v>75.2</x:v>
       </x:c>
       <x:c r="E82" s="151">
-        <x:v>75.2</x:v>
+        <x:v>76.9</x:v>
       </x:c>
       <x:c r="F82" s="152">
-        <x:v>27304</x:v>
+        <x:v>2426</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:6">
@@ -10897,19 +10903,19 @@
         <x:v>233</x:v>
       </x:c>
       <x:c r="B83" s="150">
-        <x:v>76</x:v>
+        <x:v>75.1</x:v>
       </x:c>
       <x:c r="C83" s="150">
-        <x:v>77.6</x:v>
+        <x:v>76.4</x:v>
       </x:c>
       <x:c r="D83" s="150">
-        <x:v>76</x:v>
+        <x:v>75.1</x:v>
       </x:c>
       <x:c r="E83" s="151">
-        <x:v>76.1</x:v>
+        <x:v>75.6</x:v>
       </x:c>
       <x:c r="F83" s="152">
-        <x:v>1907</x:v>
+        <x:v>903</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:6">
@@ -10917,19 +10923,19 @@
         <x:v>234</x:v>
       </x:c>
       <x:c r="B84" s="150">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C84" s="150">
-        <x:v>77.8</x:v>
+        <x:v>77.4</x:v>
       </x:c>
       <x:c r="D84" s="150">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E84" s="151">
-        <x:v>76</x:v>
+        <x:v>75.2</x:v>
       </x:c>
       <x:c r="F84" s="152">
-        <x:v>2519</x:v>
+        <x:v>27304</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:6">
@@ -10937,19 +10943,19 @@
         <x:v>235</x:v>
       </x:c>
       <x:c r="B85" s="150">
-        <x:v>76.2</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C85" s="150">
-        <x:v>77.8</x:v>
+        <x:v>77.6</x:v>
       </x:c>
       <x:c r="D85" s="150">
-        <x:v>74.2</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E85" s="151">
-        <x:v>76.4</x:v>
+        <x:v>76.1</x:v>
       </x:c>
       <x:c r="F85" s="152">
-        <x:v>16937</x:v>
+        <x:v>1907</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:6">
@@ -10957,19 +10963,19 @@
         <x:v>236</x:v>
       </x:c>
       <x:c r="B86" s="150">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C86" s="150">
-        <x:v>78.5</x:v>
+        <x:v>77.8</x:v>
       </x:c>
       <x:c r="D86" s="150">
         <x:v>76</x:v>
       </x:c>
       <x:c r="E86" s="151">
-        <x:v>77.2</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="F86" s="152">
-        <x:v>1859</x:v>
+        <x:v>2519</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:6">
@@ -10977,19 +10983,19 @@
         <x:v>237</x:v>
       </x:c>
       <x:c r="B87" s="150">
-        <x:v>78.7</x:v>
+        <x:v>76.2</x:v>
       </x:c>
       <x:c r="C87" s="150">
-        <x:v>79.7</x:v>
+        <x:v>77.8</x:v>
       </x:c>
       <x:c r="D87" s="150">
-        <x:v>78.3</x:v>
+        <x:v>74.2</x:v>
       </x:c>
       <x:c r="E87" s="151">
-        <x:v>78.5</x:v>
+        <x:v>76.4</x:v>
       </x:c>
       <x:c r="F87" s="152">
-        <x:v>5444</x:v>
+        <x:v>16937</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:6">
@@ -10997,19 +11003,19 @@
         <x:v>238</x:v>
       </x:c>
       <x:c r="B88" s="150">
-        <x:v>77.1</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C88" s="150">
-        <x:v>79.5</x:v>
+        <x:v>78.5</x:v>
       </x:c>
       <x:c r="D88" s="150">
-        <x:v>77.1</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E88" s="151">
-        <x:v>78.5</x:v>
+        <x:v>77.2</x:v>
       </x:c>
       <x:c r="F88" s="152">
-        <x:v>1565</x:v>
+        <x:v>1859</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:6">
@@ -11017,19 +11023,19 @@
         <x:v>239</x:v>
       </x:c>
       <x:c r="B89" s="150">
-        <x:v>79.4</x:v>
+        <x:v>78.7</x:v>
       </x:c>
       <x:c r="C89" s="150">
-        <x:v>79.4</x:v>
+        <x:v>79.7</x:v>
       </x:c>
       <x:c r="D89" s="150">
-        <x:v>76.3</x:v>
+        <x:v>78.3</x:v>
       </x:c>
       <x:c r="E89" s="151">
-        <x:v>77</x:v>
+        <x:v>78.5</x:v>
       </x:c>
       <x:c r="F89" s="152">
-        <x:v>3438</x:v>
+        <x:v>5444</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:6">
@@ -11037,19 +11043,19 @@
         <x:v>240</x:v>
       </x:c>
       <x:c r="B90" s="150">
-        <x:v>77</x:v>
+        <x:v>77.1</x:v>
       </x:c>
       <x:c r="C90" s="150">
-        <x:v>79.9</x:v>
+        <x:v>79.5</x:v>
       </x:c>
       <x:c r="D90" s="150">
-        <x:v>76.1</x:v>
+        <x:v>77.1</x:v>
       </x:c>
       <x:c r="E90" s="151">
-        <x:v>77.2</x:v>
+        <x:v>78.5</x:v>
       </x:c>
       <x:c r="F90" s="152">
-        <x:v>6282</x:v>
+        <x:v>1565</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:6">
@@ -11057,19 +11063,19 @@
         <x:v>241</x:v>
       </x:c>
       <x:c r="B91" s="150">
-        <x:v>81.2</x:v>
+        <x:v>79.4</x:v>
       </x:c>
       <x:c r="C91" s="150">
-        <x:v>81.2</x:v>
+        <x:v>79.4</x:v>
       </x:c>
       <x:c r="D91" s="150">
-        <x:v>78.6</x:v>
+        <x:v>76.3</x:v>
       </x:c>
       <x:c r="E91" s="151">
-        <x:v>78.6</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F91" s="152">
-        <x:v>5831</x:v>
+        <x:v>3438</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:6">
@@ -11077,19 +11083,19 @@
         <x:v>242</x:v>
       </x:c>
       <x:c r="B92" s="150">
-        <x:v>78.2</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C92" s="150">
-        <x:v>81.2</x:v>
+        <x:v>79.9</x:v>
       </x:c>
       <x:c r="D92" s="150">
-        <x:v>78.2</x:v>
+        <x:v>76.1</x:v>
       </x:c>
       <x:c r="E92" s="151">
-        <x:v>78.6</x:v>
+        <x:v>77.2</x:v>
       </x:c>
       <x:c r="F92" s="152">
-        <x:v>6329</x:v>
+        <x:v>6282</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:6">
@@ -11097,19 +11103,19 @@
         <x:v>243</x:v>
       </x:c>
       <x:c r="B93" s="150">
-        <x:v>81.5</x:v>
+        <x:v>81.2</x:v>
       </x:c>
       <x:c r="C93" s="150">
-        <x:v>81.5</x:v>
+        <x:v>81.2</x:v>
       </x:c>
       <x:c r="D93" s="150">
-        <x:v>76.7</x:v>
+        <x:v>78.6</x:v>
       </x:c>
       <x:c r="E93" s="151">
-        <x:v>78</x:v>
+        <x:v>78.6</x:v>
       </x:c>
       <x:c r="F93" s="152">
-        <x:v>34698</x:v>
+        <x:v>5831</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:6">
@@ -11117,19 +11123,19 @@
         <x:v>244</x:v>
       </x:c>
       <x:c r="B94" s="150">
-        <x:v>77.5</x:v>
+        <x:v>78.2</x:v>
       </x:c>
       <x:c r="C94" s="150">
-        <x:v>82.5</x:v>
+        <x:v>81.2</x:v>
       </x:c>
       <x:c r="D94" s="150">
-        <x:v>76.2</x:v>
+        <x:v>78.2</x:v>
       </x:c>
       <x:c r="E94" s="151">
-        <x:v>77.4</x:v>
+        <x:v>78.6</x:v>
       </x:c>
       <x:c r="F94" s="152">
-        <x:v>14094</x:v>
+        <x:v>6329</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:6">
@@ -11137,19 +11143,19 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="B95" s="150">
-        <x:v>79.6</x:v>
+        <x:v>81.5</x:v>
       </x:c>
       <x:c r="C95" s="150">
-        <x:v>82.6</x:v>
+        <x:v>81.5</x:v>
       </x:c>
       <x:c r="D95" s="150">
-        <x:v>77.4</x:v>
+        <x:v>76.7</x:v>
       </x:c>
       <x:c r="E95" s="151">
-        <x:v>77.9</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F95" s="152">
-        <x:v>8603</x:v>
+        <x:v>34698</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:6">
@@ -11157,19 +11163,19 @@
         <x:v>246</x:v>
       </x:c>
       <x:c r="B96" s="150">
-        <x:v>82.9</x:v>
+        <x:v>77.5</x:v>
       </x:c>
       <x:c r="C96" s="150">
-        <x:v>82.9</x:v>
+        <x:v>82.5</x:v>
       </x:c>
       <x:c r="D96" s="150">
-        <x:v>78.6</x:v>
+        <x:v>76.2</x:v>
       </x:c>
       <x:c r="E96" s="151">
-        <x:v>81.1</x:v>
+        <x:v>77.4</x:v>
       </x:c>
       <x:c r="F96" s="152">
-        <x:v>7097</x:v>
+        <x:v>14094</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:6">
@@ -11177,19 +11183,19 @@
         <x:v>247</x:v>
       </x:c>
       <x:c r="B97" s="150">
-        <x:v>81</x:v>
+        <x:v>79.6</x:v>
       </x:c>
       <x:c r="C97" s="150">
-        <x:v>87.9</x:v>
+        <x:v>82.6</x:v>
       </x:c>
       <x:c r="D97" s="150">
-        <x:v>80.8</x:v>
+        <x:v>77.4</x:v>
       </x:c>
       <x:c r="E97" s="151">
-        <x:v>80.8</x:v>
+        <x:v>77.9</x:v>
       </x:c>
       <x:c r="F97" s="152">
-        <x:v>5788</x:v>
+        <x:v>8603</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:6">
@@ -11197,19 +11203,19 @@
         <x:v>248</x:v>
       </x:c>
       <x:c r="B98" s="150">
-        <x:v>80.5</x:v>
+        <x:v>82.9</x:v>
       </x:c>
       <x:c r="C98" s="150">
-        <x:v>83</x:v>
+        <x:v>82.9</x:v>
       </x:c>
       <x:c r="D98" s="150">
-        <x:v>80.5</x:v>
+        <x:v>78.6</x:v>
       </x:c>
       <x:c r="E98" s="151">
-        <x:v>81.5</x:v>
+        <x:v>81.1</x:v>
       </x:c>
       <x:c r="F98" s="152">
-        <x:v>13445</x:v>
+        <x:v>7097</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:6">
@@ -11217,19 +11223,19 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="B99" s="150">
-        <x:v>83.5</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C99" s="150">
-        <x:v>83.5</x:v>
+        <x:v>87.9</x:v>
       </x:c>
       <x:c r="D99" s="150">
-        <x:v>80.2</x:v>
+        <x:v>80.8</x:v>
       </x:c>
       <x:c r="E99" s="151">
-        <x:v>80.5</x:v>
+        <x:v>80.8</x:v>
       </x:c>
       <x:c r="F99" s="152">
-        <x:v>7303</x:v>
+        <x:v>5788</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:6">
@@ -11237,19 +11243,19 @@
         <x:v>250</x:v>
       </x:c>
       <x:c r="B100" s="150">
-        <x:v>83.5</x:v>
+        <x:v>80.5</x:v>
       </x:c>
       <x:c r="C100" s="150">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D100" s="150">
-        <x:v>81.7</x:v>
+        <x:v>80.5</x:v>
       </x:c>
       <x:c r="E100" s="151">
-        <x:v>82</x:v>
+        <x:v>81.5</x:v>
       </x:c>
       <x:c r="F100" s="152">
-        <x:v>17348</x:v>
+        <x:v>13445</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:6">
@@ -11260,16 +11266,16 @@
         <x:v>83.5</x:v>
       </x:c>
       <x:c r="C101" s="150">
-        <x:v>84.2</x:v>
+        <x:v>83.5</x:v>
       </x:c>
       <x:c r="D101" s="150">
-        <x:v>82</x:v>
+        <x:v>80.2</x:v>
       </x:c>
       <x:c r="E101" s="151">
-        <x:v>83</x:v>
+        <x:v>80.5</x:v>
       </x:c>
       <x:c r="F101" s="152">
-        <x:v>25609</x:v>
+        <x:v>7303</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:6">
@@ -11277,19 +11283,19 @@
         <x:v>252</x:v>
       </x:c>
       <x:c r="B102" s="150">
-        <x:v>79</x:v>
+        <x:v>83.5</x:v>
       </x:c>
       <x:c r="C102" s="150">
-        <x:v>91</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D102" s="150">
-        <x:v>79</x:v>
+        <x:v>81.7</x:v>
       </x:c>
       <x:c r="E102" s="151">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="F102" s="152">
-        <x:v>49546</x:v>
+        <x:v>17348</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:6">
@@ -11297,19 +11303,19 @@
         <x:v>253</x:v>
       </x:c>
       <x:c r="B103" s="150">
-        <x:v>88</x:v>
+        <x:v>83.5</x:v>
       </x:c>
       <x:c r="C103" s="150">
-        <x:v>88</x:v>
+        <x:v>84.2</x:v>
       </x:c>
       <x:c r="D103" s="150">
-        <x:v>74</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E103" s="151">
-        <x:v>79</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="F103" s="152">
-        <x:v>249411</x:v>
+        <x:v>25609</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:6">
@@ -11317,19 +11323,19 @@
         <x:v>254</x:v>
       </x:c>
       <x:c r="B104" s="150">
-        <x:v>116.4</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C104" s="150">
-        <x:v>119.2</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D104" s="150">
-        <x:v>111</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E104" s="151">
-        <x:v>113</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="F104" s="152">
-        <x:v>7610</x:v>
+        <x:v>49546</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:6">
@@ -11337,19 +11343,19 @@
         <x:v>255</x:v>
       </x:c>
       <x:c r="B105" s="150">
-        <x:v>111</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C105" s="150">
-        <x:v>119.2</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D105" s="150">
-        <x:v>110.2</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E105" s="151">
-        <x:v>116</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F105" s="152">
-        <x:v>19918</x:v>
+        <x:v>249411</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:6">
@@ -11357,19 +11363,19 @@
         <x:v>256</x:v>
       </x:c>
       <x:c r="B106" s="150">
+        <x:v>116.4</x:v>
+      </x:c>
+      <x:c r="C106" s="150">
+        <x:v>119.2</x:v>
+      </x:c>
+      <x:c r="D106" s="150">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="C106" s="150">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="D106" s="150">
-        <x:v>105</x:v>
-      </x:c>
       <x:c r="E106" s="151">
-        <x:v>110.2</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="F106" s="152">
-        <x:v>3178</x:v>
+        <x:v>7610</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:6">
@@ -11377,19 +11383,19 @@
         <x:v>257</x:v>
       </x:c>
       <x:c r="B107" s="150">
-        <x:v>112</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C107" s="150">
-        <x:v>112</x:v>
+        <x:v>119.2</x:v>
       </x:c>
       <x:c r="D107" s="150">
-        <x:v>107</x:v>
+        <x:v>110.2</x:v>
       </x:c>
       <x:c r="E107" s="151">
-        <x:v>111.8</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="F107" s="152">
-        <x:v>5002</x:v>
+        <x:v>19918</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:6">
@@ -11397,19 +11403,19 @@
         <x:v>258</x:v>
       </x:c>
       <x:c r="B108" s="150">
-        <x:v>113</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C108" s="150">
-        <x:v>113</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D108" s="150">
-        <x:v>108.2</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E108" s="151">
-        <x:v>111</x:v>
+        <x:v>110.2</x:v>
       </x:c>
       <x:c r="F108" s="152">
-        <x:v>9583</x:v>
+        <x:v>3178</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:6">
@@ -11417,19 +11423,19 @@
         <x:v>259</x:v>
       </x:c>
       <x:c r="B109" s="150">
-        <x:v>113</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C109" s="150">
-        <x:v>119.2</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D109" s="150">
-        <x:v>112.8</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E109" s="151">
-        <x:v>113</x:v>
+        <x:v>111.8</x:v>
       </x:c>
       <x:c r="F109" s="152">
-        <x:v>16100</x:v>
+        <x:v>5002</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:6">
@@ -11437,19 +11443,19 @@
         <x:v>260</x:v>
       </x:c>
       <x:c r="B110" s="150">
-        <x:v>106.2</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C110" s="150">
-        <x:v>119.8</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D110" s="150">
-        <x:v>106.2</x:v>
+        <x:v>108.2</x:v>
       </x:c>
       <x:c r="E110" s="151">
-        <x:v>112</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="F110" s="152">
-        <x:v>33742</x:v>
+        <x:v>9583</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:6">
@@ -11457,19 +11463,19 @@
         <x:v>261</x:v>
       </x:c>
       <x:c r="B111" s="150">
-        <x:v>104.4</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C111" s="150">
-        <x:v>105</x:v>
+        <x:v>119.2</x:v>
       </x:c>
       <x:c r="D111" s="150">
-        <x:v>102</x:v>
+        <x:v>112.8</x:v>
       </x:c>
       <x:c r="E111" s="151">
-        <x:v>105</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="F111" s="152">
-        <x:v>2726</x:v>
+        <x:v>16100</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:6">
@@ -11477,19 +11483,19 @@
         <x:v>262</x:v>
       </x:c>
       <x:c r="B112" s="150">
-        <x:v>104</x:v>
+        <x:v>106.2</x:v>
       </x:c>
       <x:c r="C112" s="150">
-        <x:v>105</x:v>
+        <x:v>119.8</x:v>
       </x:c>
       <x:c r="D112" s="150">
-        <x:v>100</x:v>
+        <x:v>106.2</x:v>
       </x:c>
       <x:c r="E112" s="151">
-        <x:v>104.4</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="F112" s="152">
-        <x:v>3713</x:v>
+        <x:v>33742</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:6">
@@ -11497,19 +11503,19 @@
         <x:v>263</x:v>
       </x:c>
       <x:c r="B113" s="150">
-        <x:v>98</x:v>
+        <x:v>104.4</x:v>
       </x:c>
       <x:c r="C113" s="150">
         <x:v>105</x:v>
       </x:c>
       <x:c r="D113" s="150">
-        <x:v>98</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E113" s="151">
         <x:v>105</x:v>
       </x:c>
       <x:c r="F113" s="152">
-        <x:v>9937</x:v>
+        <x:v>2726</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:6">
@@ -11517,19 +11523,19 @@
         <x:v>264</x:v>
       </x:c>
       <x:c r="B114" s="150">
-        <x:v>95.6</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C114" s="150">
-        <x:v>98.5</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D114" s="150">
-        <x:v>93</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E114" s="151">
-        <x:v>97.7</x:v>
+        <x:v>104.4</x:v>
       </x:c>
       <x:c r="F114" s="152">
-        <x:v>914</x:v>
+        <x:v>3713</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:6">
@@ -11537,19 +11543,19 @@
         <x:v>265</x:v>
       </x:c>
       <x:c r="B115" s="150">
-        <x:v>95.6</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C115" s="150">
-        <x:v>96</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D115" s="150">
-        <x:v>94</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E115" s="151">
-        <x:v>96</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F115" s="152">
-        <x:v>1545</x:v>
+        <x:v>9937</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:6">
@@ -11557,19 +11563,19 @@
         <x:v>266</x:v>
       </x:c>
       <x:c r="B116" s="150">
-        <x:v>95.2</x:v>
+        <x:v>95.6</x:v>
       </x:c>
       <x:c r="C116" s="150">
-        <x:v>95.6</x:v>
+        <x:v>98.5</x:v>
       </x:c>
       <x:c r="D116" s="150">
-        <x:v>93.01</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E116" s="151">
-        <x:v>95.6</x:v>
+        <x:v>97.7</x:v>
       </x:c>
       <x:c r="F116" s="152">
-        <x:v>2495</x:v>
+        <x:v>914</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:6">
@@ -11580,16 +11586,16 @@
         <x:v>95.6</x:v>
       </x:c>
       <x:c r="C117" s="150">
-        <x:v>95.6</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D117" s="150">
-        <x:v>94.2</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E117" s="151">
-        <x:v>95.6</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="F117" s="152">
-        <x:v>2564</x:v>
+        <x:v>1545</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:6">
@@ -11597,19 +11603,19 @@
         <x:v>268</x:v>
       </x:c>
       <x:c r="B118" s="150">
-        <x:v>93.2</x:v>
+        <x:v>95.2</x:v>
       </x:c>
       <x:c r="C118" s="150">
-        <x:v>96.8</x:v>
+        <x:v>95.6</x:v>
       </x:c>
       <x:c r="D118" s="150">
-        <x:v>93.2</x:v>
+        <x:v>93.01</x:v>
       </x:c>
       <x:c r="E118" s="151">
         <x:v>95.6</x:v>
       </x:c>
       <x:c r="F118" s="152">
-        <x:v>17572</x:v>
+        <x:v>2495</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:6">
@@ -11617,19 +11623,19 @@
         <x:v>269</x:v>
       </x:c>
       <x:c r="B119" s="150">
-        <x:v>91</x:v>
+        <x:v>95.6</x:v>
       </x:c>
       <x:c r="C119" s="150">
-        <x:v>99.4</x:v>
+        <x:v>95.6</x:v>
       </x:c>
       <x:c r="D119" s="150">
-        <x:v>91</x:v>
+        <x:v>94.2</x:v>
       </x:c>
       <x:c r="E119" s="151">
-        <x:v>92.8</x:v>
+        <x:v>95.6</x:v>
       </x:c>
       <x:c r="F119" s="152">
-        <x:v>9817</x:v>
+        <x:v>2564</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:6">
@@ -11637,19 +11643,19 @@
         <x:v>270</x:v>
       </x:c>
       <x:c r="B120" s="150">
-        <x:v>90</x:v>
+        <x:v>93.2</x:v>
       </x:c>
       <x:c r="C120" s="150">
-        <x:v>91.2</x:v>
+        <x:v>96.8</x:v>
       </x:c>
       <x:c r="D120" s="150">
-        <x:v>89.2</x:v>
+        <x:v>93.2</x:v>
       </x:c>
       <x:c r="E120" s="151">
-        <x:v>91.2</x:v>
+        <x:v>95.6</x:v>
       </x:c>
       <x:c r="F120" s="152">
-        <x:v>1773</x:v>
+        <x:v>17572</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:6">
@@ -11660,16 +11666,16 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="C121" s="150">
-        <x:v>92</x:v>
+        <x:v>99.4</x:v>
       </x:c>
       <x:c r="D121" s="150">
-        <x:v>89.8</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E121" s="151">
-        <x:v>90.2</x:v>
+        <x:v>92.8</x:v>
       </x:c>
       <x:c r="F121" s="152">
-        <x:v>9883</x:v>
+        <x:v>9817</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:6">
@@ -11677,19 +11683,19 @@
         <x:v>272</x:v>
       </x:c>
       <x:c r="B122" s="150">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C122" s="150">
-        <x:v>92.6</x:v>
+        <x:v>91.2</x:v>
       </x:c>
       <x:c r="D122" s="150">
-        <x:v>87</x:v>
+        <x:v>89.2</x:v>
       </x:c>
       <x:c r="E122" s="151">
-        <x:v>91</x:v>
+        <x:v>91.2</x:v>
       </x:c>
       <x:c r="F122" s="152">
-        <x:v>13360</x:v>
+        <x:v>1773</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:6">
@@ -11697,19 +11703,19 @@
         <x:v>273</x:v>
       </x:c>
       <x:c r="B123" s="150">
-        <x:v>87.4</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C123" s="150">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D123" s="150">
         <x:v>89.8</x:v>
       </x:c>
-      <x:c r="D123" s="150">
-        <x:v>86</x:v>
-      </x:c>
       <x:c r="E123" s="151">
-        <x:v>89.8</x:v>
+        <x:v>90.2</x:v>
       </x:c>
       <x:c r="F123" s="152">
-        <x:v>5989</x:v>
+        <x:v>9883</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:6">
@@ -11720,16 +11726,16 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="C124" s="150">
-        <x:v>89.6</x:v>
+        <x:v>92.6</x:v>
       </x:c>
       <x:c r="D124" s="150">
-        <x:v>86.8</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E124" s="151">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="F124" s="152">
-        <x:v>12060</x:v>
+        <x:v>13360</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:6">
@@ -11737,19 +11743,19 @@
         <x:v>275</x:v>
       </x:c>
       <x:c r="B125" s="150">
-        <x:v>89.6</x:v>
+        <x:v>87.4</x:v>
       </x:c>
       <x:c r="C125" s="150">
-        <x:v>90.4</x:v>
+        <x:v>89.8</x:v>
       </x:c>
       <x:c r="D125" s="150">
-        <x:v>89</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E125" s="151">
-        <x:v>89</x:v>
+        <x:v>89.8</x:v>
       </x:c>
       <x:c r="F125" s="152">
-        <x:v>2264</x:v>
+        <x:v>5989</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:6">
@@ -11757,19 +11763,19 @@
         <x:v>276</x:v>
       </x:c>
       <x:c r="B126" s="150">
-        <x:v>90.8</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C126" s="150">
-        <x:v>93.4</x:v>
+        <x:v>89.6</x:v>
       </x:c>
       <x:c r="D126" s="150">
-        <x:v>87.2</x:v>
+        <x:v>86.8</x:v>
       </x:c>
       <x:c r="E126" s="151">
-        <x:v>89.6</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F126" s="152">
-        <x:v>16000</x:v>
+        <x:v>12060</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:6">
@@ -11777,19 +11783,19 @@
         <x:v>277</x:v>
       </x:c>
       <x:c r="B127" s="150">
-        <x:v>91</x:v>
+        <x:v>89.6</x:v>
       </x:c>
       <x:c r="C127" s="150">
-        <x:v>94</x:v>
+        <x:v>90.4</x:v>
       </x:c>
       <x:c r="D127" s="150">
-        <x:v>89.2</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E127" s="151">
-        <x:v>90.8</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F127" s="152">
-        <x:v>5670</x:v>
+        <x:v>2264</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:6">
@@ -11797,19 +11803,19 @@
         <x:v>278</x:v>
       </x:c>
       <x:c r="B128" s="150">
-        <x:v>91</x:v>
+        <x:v>90.8</x:v>
       </x:c>
       <x:c r="C128" s="150">
-        <x:v>94</x:v>
+        <x:v>93.4</x:v>
       </x:c>
       <x:c r="D128" s="150">
-        <x:v>90.6</x:v>
+        <x:v>87.2</x:v>
       </x:c>
       <x:c r="E128" s="151">
-        <x:v>91</x:v>
+        <x:v>89.6</x:v>
       </x:c>
       <x:c r="F128" s="152">
-        <x:v>8937</x:v>
+        <x:v>16000</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:6">
@@ -11817,19 +11823,19 @@
         <x:v>279</x:v>
       </x:c>
       <x:c r="B129" s="150">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C129" s="150">
-        <x:v>93.2</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D129" s="150">
-        <x:v>90</x:v>
+        <x:v>89.2</x:v>
       </x:c>
       <x:c r="E129" s="151">
-        <x:v>91</x:v>
+        <x:v>90.8</x:v>
       </x:c>
       <x:c r="F129" s="152">
-        <x:v>35625</x:v>
+        <x:v>5670</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:6">
@@ -11837,19 +11843,19 @@
         <x:v>280</x:v>
       </x:c>
       <x:c r="B130" s="150">
-        <x:v>93.4</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C130" s="150">
-        <x:v>93.4</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D130" s="150">
-        <x:v>89.2</x:v>
+        <x:v>90.6</x:v>
       </x:c>
       <x:c r="E130" s="151">
-        <x:v>89.4</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="F130" s="152">
-        <x:v>9629</x:v>
+        <x:v>8937</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:6">
@@ -11857,19 +11863,19 @@
         <x:v>281</x:v>
       </x:c>
       <x:c r="B131" s="150">
-        <x:v>88.6</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C131" s="150">
-        <x:v>93.8</x:v>
+        <x:v>93.2</x:v>
       </x:c>
       <x:c r="D131" s="150">
-        <x:v>87.2</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E131" s="151">
-        <x:v>93.4</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="F131" s="152">
-        <x:v>5454</x:v>
+        <x:v>35625</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:6">
@@ -11877,19 +11883,19 @@
         <x:v>282</x:v>
       </x:c>
       <x:c r="B132" s="150">
-        <x:v>89</x:v>
+        <x:v>93.4</x:v>
       </x:c>
       <x:c r="C132" s="150">
-        <x:v>91.4</x:v>
+        <x:v>93.4</x:v>
       </x:c>
       <x:c r="D132" s="150">
-        <x:v>85.2</x:v>
+        <x:v>89.2</x:v>
       </x:c>
       <x:c r="E132" s="151">
-        <x:v>87.2</x:v>
+        <x:v>89.4</x:v>
       </x:c>
       <x:c r="F132" s="152">
-        <x:v>7997</x:v>
+        <x:v>9629</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:6">
@@ -11897,19 +11903,19 @@
         <x:v>283</x:v>
       </x:c>
       <x:c r="B133" s="150">
-        <x:v>91.4</x:v>
+        <x:v>88.6</x:v>
       </x:c>
       <x:c r="C133" s="150">
-        <x:v>91.4</x:v>
+        <x:v>93.8</x:v>
       </x:c>
       <x:c r="D133" s="150">
-        <x:v>88.4</x:v>
+        <x:v>87.2</x:v>
       </x:c>
       <x:c r="E133" s="151">
-        <x:v>89</x:v>
+        <x:v>93.4</x:v>
       </x:c>
       <x:c r="F133" s="152">
-        <x:v>2637</x:v>
+        <x:v>5454</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:6">
@@ -11917,19 +11923,19 @@
         <x:v>284</x:v>
       </x:c>
       <x:c r="B134" s="150">
-        <x:v>88.8</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C134" s="150">
-        <x:v>88.8</x:v>
+        <x:v>91.4</x:v>
       </x:c>
       <x:c r="D134" s="150">
         <x:v>85.2</x:v>
       </x:c>
       <x:c r="E134" s="151">
-        <x:v>88.2</x:v>
+        <x:v>87.2</x:v>
       </x:c>
       <x:c r="F134" s="152">
-        <x:v>8604</x:v>
+        <x:v>7997</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:6">
@@ -11937,19 +11943,19 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="B135" s="150">
-        <x:v>90.8</x:v>
+        <x:v>91.4</x:v>
       </x:c>
       <x:c r="C135" s="150">
-        <x:v>90.8</x:v>
+        <x:v>91.4</x:v>
       </x:c>
       <x:c r="D135" s="150">
-        <x:v>88.2</x:v>
+        <x:v>88.4</x:v>
       </x:c>
       <x:c r="E135" s="151">
-        <x:v>89.6</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F135" s="152">
-        <x:v>4162</x:v>
+        <x:v>2637</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:6">
@@ -11957,19 +11963,19 @@
         <x:v>286</x:v>
       </x:c>
       <x:c r="B136" s="150">
-        <x:v>91.6</x:v>
+        <x:v>88.8</x:v>
       </x:c>
       <x:c r="C136" s="150">
-        <x:v>91.6</x:v>
+        <x:v>88.8</x:v>
       </x:c>
       <x:c r="D136" s="150">
-        <x:v>88</x:v>
+        <x:v>85.2</x:v>
       </x:c>
       <x:c r="E136" s="151">
-        <x:v>90</x:v>
+        <x:v>88.2</x:v>
       </x:c>
       <x:c r="F136" s="152">
-        <x:v>29964</x:v>
+        <x:v>8604</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:6">
@@ -11986,10 +11992,10 @@
         <x:v>88.2</x:v>
       </x:c>
       <x:c r="E137" s="151">
-        <x:v>89.8</x:v>
+        <x:v>89.6</x:v>
       </x:c>
       <x:c r="F137" s="152">
-        <x:v>13315</x:v>
+        <x:v>4162</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:6">
@@ -11997,19 +12003,19 @@
         <x:v>288</x:v>
       </x:c>
       <x:c r="B138" s="150">
-        <x:v>91.2</x:v>
+        <x:v>91.6</x:v>
       </x:c>
       <x:c r="C138" s="150">
         <x:v>91.6</x:v>
       </x:c>
       <x:c r="D138" s="150">
-        <x:v>89.4</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E138" s="151">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F138" s="152">
-        <x:v>9335</x:v>
+        <x:v>29964</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:6">
@@ -12017,19 +12023,19 @@
         <x:v>289</x:v>
       </x:c>
       <x:c r="B139" s="150">
-        <x:v>92</x:v>
+        <x:v>90.8</x:v>
       </x:c>
       <x:c r="C139" s="150">
-        <x:v>92.98</x:v>
+        <x:v>90.8</x:v>
       </x:c>
       <x:c r="D139" s="150">
-        <x:v>91.2</x:v>
+        <x:v>88.2</x:v>
       </x:c>
       <x:c r="E139" s="151">
-        <x:v>91.3</x:v>
+        <x:v>89.8</x:v>
       </x:c>
       <x:c r="F139" s="152">
-        <x:v>13836</x:v>
+        <x:v>13315</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:6">
@@ -12037,19 +12043,19 @@
         <x:v>290</x:v>
       </x:c>
       <x:c r="B140" s="150">
-        <x:v>91.35</x:v>
+        <x:v>91.2</x:v>
       </x:c>
       <x:c r="C140" s="150">
-        <x:v>93.8</x:v>
+        <x:v>91.6</x:v>
       </x:c>
       <x:c r="D140" s="150">
-        <x:v>91.3</x:v>
+        <x:v>89.4</x:v>
       </x:c>
       <x:c r="E140" s="151">
-        <x:v>91.5</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="F140" s="152">
-        <x:v>66626</x:v>
+        <x:v>9335</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:6">
@@ -12057,18 +12063,58 @@
         <x:v>291</x:v>
       </x:c>
       <x:c r="B141" s="150">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C141" s="150">
+        <x:v>92.98</x:v>
+      </x:c>
+      <x:c r="D141" s="150">
+        <x:v>91.2</x:v>
+      </x:c>
+      <x:c r="E141" s="151">
+        <x:v>91.3</x:v>
+      </x:c>
+      <x:c r="F141" s="152">
+        <x:v>13836</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142" spans="1:6">
+      <x:c r="A142" s="149" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="B142" s="150">
+        <x:v>91.35</x:v>
+      </x:c>
+      <x:c r="C142" s="150">
+        <x:v>93.8</x:v>
+      </x:c>
+      <x:c r="D142" s="150">
+        <x:v>91.3</x:v>
+      </x:c>
+      <x:c r="E142" s="151">
+        <x:v>91.5</x:v>
+      </x:c>
+      <x:c r="F142" s="152">
+        <x:v>66626</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143" spans="1:6">
+      <x:c r="A143" s="149" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="B143" s="150">
         <x:v>91.97</x:v>
       </x:c>
-      <x:c r="C141" s="150">
+      <x:c r="C143" s="150">
         <x:v>93.99</x:v>
       </x:c>
-      <x:c r="D141" s="150">
+      <x:c r="D143" s="150">
         <x:v>89.03</x:v>
       </x:c>
-      <x:c r="E141" s="151">
+      <x:c r="E143" s="151">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="F141" s="152">
+      <x:c r="F143" s="152">
         <x:v>211924</x:v>
       </x:c>
     </x:row>
